--- a/hca-to-scea/test/golden/ERP121676_1.xlsx
+++ b/hca-to-scea/test/golden/ERP121676_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arsenios/Documents/GitHub/hca-to-scea-tools/hca-to-scea/test/golden/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E25E15B-F71F-FD4A-B2C0-8F5E576DD3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B08BB4C-7034-9A49-A9EE-9E33C41B0E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11200" yWindow="6340" windowWidth="28800" windowHeight="16620" firstSheet="7" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11200" yWindow="6340" windowWidth="28800" windowHeight="16620" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="1309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2663" uniqueCount="1304">
   <si>
     <t>PROJECT LABEL (Required)</t>
   </si>
@@ -1571,21 +1571,6 @@
   </si>
   <si>
     <t>biopsy</t>
-  </si>
-  <si>
-    <t>collection_protocol_ipscs</t>
-  </si>
-  <si>
-    <t>Feeder-free human iPSCs were obtained from the HipSci project. Lines were thawed onto tissue culture-treated plates coated with 10 μg/mL VitronectinXF using complete Essential 8 (E8) medium and 10 μM Rock inhibitor. Cells were expanded in E8 medium for 2 passages using 0.5 μM EDTA pH 8.0 for cell dissociation.</t>
-  </si>
-  <si>
-    <t>10.1093/nar/gkw928||10.1038/nature22403</t>
-  </si>
-  <si>
-    <t>collecting specimen from organism</t>
-  </si>
-  <si>
-    <t>OBI:0600005</t>
   </si>
   <si>
     <t>SPECIMEN FROM ORGANISM ID (Required)</t>
@@ -5765,13 +5750,13 @@
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>117</v>
@@ -5783,16 +5768,16 @@
         <v>454</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>458</v>
@@ -5813,13 +5798,13 @@
         <v>463</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="85">
@@ -5842,16 +5827,16 @@
         <v>469</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>470</v>
@@ -5872,13 +5857,13 @@
         <v>475</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="85">
@@ -5897,16 +5882,16 @@
         <v>479</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>480</v>
@@ -5927,72 +5912,72 @@
         <v>485</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="3" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>900</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>901</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>902</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>903</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>907</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>911</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="30" customHeight="1">
@@ -6020,35 +6005,35 @@
     </row>
     <row r="6" spans="1:26" ht="328">
       <c r="A6" s="18" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="E6" s="47"/>
       <c r="F6" s="16"/>
       <c r="G6" s="18" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I6" s="48" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="48" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="N6" s="48"/>
       <c r="O6" s="18"/>
@@ -7079,13 +7064,13 @@
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>117</v>
@@ -7097,13 +7082,13 @@
         <v>454</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>458</v>
@@ -7216,49 +7201,49 @@
     </row>
     <row r="4" spans="1:26" hidden="1">
       <c r="A4" s="3" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>927</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>934</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>936</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>937</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>938</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="30" customHeight="1">
@@ -7282,25 +7267,25 @@
     </row>
     <row r="6" spans="1:26" ht="90">
       <c r="A6" s="49" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="18" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -8332,13 +8317,13 @@
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>117</v>
@@ -8350,22 +8335,22 @@
         <v>454</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>946</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>949</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="388">
@@ -8397,13 +8382,13 @@
         <v>64</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="153">
@@ -8431,51 +8416,51 @@
         <v>343</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="4" spans="1:12" hidden="1">
       <c r="A4" s="3" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>958</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>959</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>960</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>961</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>962</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>963</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>964</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>967</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1">
@@ -8496,22 +8481,22 @@
     </row>
     <row r="6" spans="1:12" ht="61">
       <c r="A6" s="18" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="L6" s="50">
         <v>40</v>
@@ -9553,13 +9538,13 @@
   <sheetData>
     <row r="1" spans="1:61" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>170</v>
@@ -9580,52 +9565,52 @@
         <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>655</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>183</v>
@@ -9637,25 +9622,25 @@
         <v>185</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>978</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>983</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>223</v>
@@ -9673,19 +9658,19 @@
         <v>227</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>228</v>
@@ -9765,10 +9750,10 @@
         <v>252</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>278</v>
@@ -9780,40 +9765,40 @@
         <v>64</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>690</v>
-      </c>
       <c r="Z2" s="2" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>63</v>
@@ -9822,7 +9807,7 @@
         <v>64</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="AD2" s="2" t="s">
         <v>63</v>
@@ -9831,16 +9816,16 @@
         <v>64</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="AJ2" s="2" t="s">
         <v>280</v>
@@ -9944,10 +9929,10 @@
         <v>298</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>332</v>
@@ -9959,37 +9944,37 @@
         <v>332</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>715</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>305</v>
@@ -10001,25 +9986,25 @@
         <v>305</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>337</v>
@@ -10092,139 +10077,139 @@
     </row>
     <row r="4" spans="1:61">
       <c r="A4" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>996</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>997</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>998</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>999</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>1000</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>1001</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>1002</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>1003</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>1004</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>1010</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>1011</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>1013</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="Y4" s="3" t="s">
         <v>1014</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>1015</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>1016</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AD4" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
         <v>1021</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AG4" s="3" t="s">
         <v>1022</v>
       </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AH4" s="3" t="s">
         <v>1023</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AI4" s="3" t="s">
         <v>1024</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>1025</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AK4" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AL4" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="AH4" s="3" t="s">
+      <c r="AM4" s="3" t="s">
         <v>1028</v>
       </c>
-      <c r="AI4" s="3" t="s">
+      <c r="AN4" s="3" t="s">
         <v>1029</v>
       </c>
-      <c r="AJ4" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="AK4" s="3" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AL4" s="3" t="s">
-        <v>1032</v>
-      </c>
-      <c r="AM4" s="3" t="s">
-        <v>1033</v>
-      </c>
-      <c r="AN4" s="3" t="s">
-        <v>1034</v>
-      </c>
       <c r="AO4" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="AP4" s="3" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="AQ4" s="3" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="AR4" s="3" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="AS4" s="3" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="AT4" s="3" t="s">
         <v>408</v>
@@ -10346,13 +10331,13 @@
     </row>
     <row r="6" spans="1:61" ht="96">
       <c r="A6" s="56" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D6" s="49">
         <v>9606</v>
@@ -10360,7 +10345,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="56" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -10390,13 +10375,13 @@
         <v>427</v>
       </c>
       <c r="AC6" s="18" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="AD6" s="18" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AE6" s="18" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
@@ -10406,29 +10391,29 @@
         <v>11</v>
       </c>
       <c r="AK6" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AL6" s="50" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AM6" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AN6" s="34" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="AO6" s="18"/>
       <c r="AP6" s="33" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="AQ6" s="52" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="AR6" s="52" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="AS6" s="53" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
@@ -10449,13 +10434,13 @@
     </row>
     <row r="7" spans="1:61" ht="96">
       <c r="A7" s="56" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D7" s="49">
         <v>9606</v>
@@ -10463,7 +10448,7 @@
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="56" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
@@ -10493,13 +10478,13 @@
         <v>427</v>
       </c>
       <c r="AC7" s="18" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="AD7" s="18" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AE7" s="18" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="AF7" s="18"/>
       <c r="AG7" s="18"/>
@@ -10509,29 +10494,29 @@
         <v>11</v>
       </c>
       <c r="AK7" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AL7" s="50" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AM7" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AN7" s="34" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="AO7" s="18"/>
       <c r="AP7" s="33" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="AQ7" s="52" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="AR7" s="52" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="AS7" s="53" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="AT7" s="18"/>
       <c r="AU7" s="18"/>
@@ -10552,13 +10537,13 @@
     </row>
     <row r="8" spans="1:61" ht="96">
       <c r="A8" s="56" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D8" s="49">
         <v>9606</v>
@@ -10566,7 +10551,7 @@
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="56" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="H8" s="18"/>
       <c r="I8" s="18"/>
@@ -10596,13 +10581,13 @@
         <v>427</v>
       </c>
       <c r="AC8" s="18" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="AD8" s="18" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AE8" s="18" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="AF8" s="18"/>
       <c r="AG8" s="18"/>
@@ -10612,29 +10597,29 @@
         <v>11</v>
       </c>
       <c r="AK8" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AL8" s="50" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AM8" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AN8" s="34" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="AO8" s="18"/>
       <c r="AP8" s="33" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="AQ8" s="52" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="AR8" s="52" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="AS8" s="53" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="AT8" s="18"/>
       <c r="AU8" s="18"/>
@@ -10655,13 +10640,13 @@
     </row>
     <row r="9" spans="1:61" ht="96">
       <c r="A9" s="56" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D9" s="49">
         <v>9606</v>
@@ -10669,7 +10654,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="56" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="H9" s="18"/>
       <c r="I9" s="18"/>
@@ -10699,13 +10684,13 @@
         <v>427</v>
       </c>
       <c r="AC9" s="18" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="AD9" s="18" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AE9" s="18" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="AF9" s="18"/>
       <c r="AG9" s="18"/>
@@ -10715,29 +10700,29 @@
         <v>11</v>
       </c>
       <c r="AK9" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AL9" s="50" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AM9" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AN9" s="34" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="AO9" s="18"/>
       <c r="AP9" s="33" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="AQ9" s="52" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="AR9" s="52" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="AS9" s="53" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="AT9" s="18"/>
       <c r="AU9" s="18"/>
@@ -10758,13 +10743,13 @@
     </row>
     <row r="10" spans="1:61" ht="96">
       <c r="A10" s="56" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D10" s="49">
         <v>9606</v>
@@ -10772,7 +10757,7 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="56" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
@@ -10802,13 +10787,13 @@
         <v>427</v>
       </c>
       <c r="AC10" s="18" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="AD10" s="18" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="AE10" s="18" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="AF10" s="18"/>
       <c r="AG10" s="18"/>
@@ -10818,29 +10803,29 @@
         <v>11</v>
       </c>
       <c r="AK10" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AL10" s="50" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AM10" s="50" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AN10" s="34" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="AO10" s="18"/>
       <c r="AP10" s="33" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="AQ10" s="52" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="AR10" s="52" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="AS10" s="53" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="AT10" s="18"/>
       <c r="AU10" s="18"/>
@@ -14387,13 +14372,13 @@
   <sheetData>
     <row r="1" spans="1:51" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>117</v>
@@ -14405,139 +14390,139 @@
         <v>454</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>1086</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="2" spans="1:51" ht="388">
@@ -14560,19 +14545,19 @@
         <v>469</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>63</v>
@@ -14581,7 +14566,7 @@
         <v>64</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>290</v>
@@ -14629,13 +14614,13 @@
         <v>475</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>470</v>
@@ -14656,19 +14641,19 @@
         <v>475</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="AR2" s="2" t="s">
         <v>290</v>
@@ -14689,10 +14674,10 @@
         <v>64</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="3" spans="1:51" ht="255">
@@ -14711,37 +14696,37 @@
         <v>479</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>1113</v>
-      </c>
       <c r="Q3" s="2" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>480</v>
@@ -14780,13 +14765,13 @@
         <v>485</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>480</v>
@@ -14807,198 +14792,198 @@
         <v>485</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="AQ3" s="2" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="AU3" s="2" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="AV3" s="2" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="AX3" s="2" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="AY3" s="2" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="4" spans="1:51" hidden="1">
       <c r="A4" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>1122</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>1124</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>1125</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>1126</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>1127</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>1128</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>1129</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>1130</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>1131</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>1133</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>1134</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>1135</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>1136</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>1137</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>1138</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>1139</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>1140</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="Y4" s="3" t="s">
         <v>1141</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>1142</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>1143</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>1144</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>1145</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AD4" s="3" t="s">
         <v>1146</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
         <v>1147</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
         <v>1148</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AG4" s="3" t="s">
         <v>1149</v>
       </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AH4" s="3" t="s">
         <v>1150</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AI4" s="3" t="s">
         <v>1151</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>1152</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AK4" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AL4" s="3" t="s">
         <v>1154</v>
       </c>
-      <c r="AH4" s="3" t="s">
+      <c r="AM4" s="3" t="s">
         <v>1155</v>
       </c>
-      <c r="AI4" s="3" t="s">
+      <c r="AN4" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="AJ4" s="3" t="s">
+      <c r="AO4" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="AK4" s="3" t="s">
+      <c r="AP4" s="3" t="s">
         <v>1158</v>
       </c>
-      <c r="AL4" s="3" t="s">
+      <c r="AQ4" s="3" t="s">
         <v>1159</v>
       </c>
-      <c r="AM4" s="3" t="s">
+      <c r="AR4" s="3" t="s">
         <v>1160</v>
       </c>
-      <c r="AN4" s="3" t="s">
+      <c r="AS4" s="3" t="s">
         <v>1161</v>
       </c>
-      <c r="AO4" s="3" t="s">
+      <c r="AT4" s="3" t="s">
         <v>1162</v>
       </c>
-      <c r="AP4" s="3" t="s">
+      <c r="AU4" s="3" t="s">
         <v>1163</v>
       </c>
-      <c r="AQ4" s="3" t="s">
+      <c r="AV4" s="3" t="s">
         <v>1164</v>
       </c>
-      <c r="AR4" s="3" t="s">
+      <c r="AW4" s="3" t="s">
         <v>1165</v>
       </c>
-      <c r="AS4" s="3" t="s">
+      <c r="AX4" s="3" t="s">
         <v>1166</v>
       </c>
-      <c r="AT4" s="3" t="s">
+      <c r="AY4" s="3" t="s">
         <v>1167</v>
-      </c>
-      <c r="AU4" s="3" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AV4" s="3" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AW4" s="3" t="s">
-        <v>1170</v>
-      </c>
-      <c r="AX4" s="3" t="s">
-        <v>1171</v>
-      </c>
-      <c r="AY4" s="3" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="5" spans="1:51" ht="30" customHeight="1">
@@ -15058,19 +15043,19 @@
     </row>
     <row r="6" spans="1:51" ht="225">
       <c r="A6" s="18" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="18" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="H6" s="18">
         <v>0</v>
@@ -15080,25 +15065,25 @@
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>1172</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>1173</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>1174</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>1175</v>
+      </c>
+      <c r="P6" s="18" t="s">
         <v>1176</v>
       </c>
-      <c r="L6" s="18" t="s">
-        <v>1177</v>
-      </c>
-      <c r="M6" s="18" t="s">
-        <v>1178</v>
-      </c>
-      <c r="N6" s="18" t="s">
-        <v>1179</v>
-      </c>
-      <c r="O6" s="18" t="s">
-        <v>1180</v>
-      </c>
-      <c r="P6" s="18" t="s">
-        <v>1181</v>
-      </c>
       <c r="Q6" s="18" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
@@ -15113,13 +15098,13 @@
       <c r="AB6" s="18"/>
       <c r="AC6" s="18"/>
       <c r="AD6" s="18" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="AE6" s="18" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="AF6" s="18" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
@@ -15129,7 +15114,7 @@
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="AO6" s="18">
         <v>16</v>
@@ -16169,13 +16154,13 @@
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>117</v>
@@ -16187,40 +16172,40 @@
         <v>454</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>1191</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>1194</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="388">
@@ -16243,7 +16228,7 @@
         <v>469</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>63</v>
@@ -16252,10 +16237,10 @@
         <v>64</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>290</v>
@@ -16267,16 +16252,16 @@
         <v>64</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="272">
@@ -16295,34 +16280,34 @@
         <v>479</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>1207</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>1207</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>1209</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>1214</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>319</v>
@@ -16333,58 +16318,58 @@
     </row>
     <row r="4" spans="1:26" hidden="1">
       <c r="A4" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>1215</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>1216</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>1217</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>1218</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>1219</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>1220</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>1221</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>1222</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>1223</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>1224</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>1225</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>1226</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>1227</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>1228</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>1229</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>1230</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="30" customHeight="1">
@@ -16411,44 +16396,44 @@
     </row>
     <row r="6" spans="1:26" ht="96">
       <c r="A6" s="18" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="18" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18" t="s">
         <v>111</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="P6" s="55" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
@@ -17482,46 +17467,46 @@
   <sheetData>
     <row r="1" spans="1:30" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>1244</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1245</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1247</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>1248</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>1251</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>228</v>
@@ -17574,13 +17559,13 @@
     </row>
     <row r="2" spans="1:30" ht="107" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>63</v>
@@ -17589,22 +17574,22 @@
         <v>64</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>1256</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>1257</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>1258</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>1259</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>1260</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>1261</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>244</v>
@@ -17666,37 +17651,37 @@
     </row>
     <row r="3" spans="1:30" ht="170">
       <c r="A3" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>1264</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>1266</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>1267</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>1270</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>1271</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="s">
@@ -17750,46 +17735,46 @@
     </row>
     <row r="4" spans="1:30" hidden="1">
       <c r="A4" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>1272</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>1273</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>1274</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>1275</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>1276</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>1277</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>1278</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1282</v>
-      </c>
       <c r="L4" s="3" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>408</v>
@@ -17876,34 +17861,34 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" s="3" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
@@ -17920,39 +17905,39 @@
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="7" spans="1:30">
       <c r="A7" s="3" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
@@ -17969,39 +17954,39 @@
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="8" spans="1:30">
       <c r="A8" s="3" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -18018,39 +18003,39 @@
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="9" spans="1:30">
       <c r="A9" s="3" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
@@ -18067,39 +18052,39 @@
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="10" spans="1:30">
       <c r="A10" s="3" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
@@ -18116,39 +18101,39 @@
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
@@ -18165,39 +18150,39 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -18214,39 +18199,39 @@
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -18263,39 +18248,39 @@
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -18312,39 +18297,39 @@
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
@@ -18361,7 +18346,7 @@
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
     </row>
   </sheetData>
@@ -23918,30 +23903,16 @@
       <c r="Z6" s="28"/>
       <c r="AA6" s="28"/>
     </row>
-    <row r="7" spans="1:27" ht="70">
-      <c r="A7" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>507</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>508</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>509</v>
-      </c>
+    <row r="7" spans="1:27" ht="14">
+      <c r="A7" s="10"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>510</v>
-      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
@@ -24997,13 +24968,13 @@
   <sheetData>
     <row r="1" spans="1:60" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>170</v>
@@ -25033,22 +25004,22 @@
         <v>185</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>520</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>195</v>
@@ -25060,70 +25031,70 @@
         <v>197</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>450</v>
@@ -25206,7 +25177,7 @@
         <v>252</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>63</v>
@@ -25215,7 +25186,7 @@
         <v>64</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>63</v>
@@ -25224,7 +25195,7 @@
         <v>64</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>63</v>
@@ -25233,7 +25204,7 @@
         <v>64</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>63</v>
@@ -25242,34 +25213,34 @@
         <v>64</v>
       </c>
       <c r="V2" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>260</v>
@@ -25281,10 +25252,10 @@
         <v>64</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="AK2" s="2" t="s">
         <v>470</v>
@@ -25391,25 +25362,25 @@
         <v>305</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>315</v>
@@ -25418,34 +25389,34 @@
         <v>316</v>
       </c>
       <c r="V3" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>310</v>
@@ -25457,7 +25428,7 @@
         <v>310</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>321</v>
@@ -25529,130 +25500,130 @@
     </row>
     <row r="4" spans="1:60">
       <c r="A4" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="Y4" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AD4" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AG4" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AH4" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AI4" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AK4" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AL4" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="AH4" s="3" t="s">
+      <c r="AM4" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="AI4" s="3" t="s">
+      <c r="AN4" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="AJ4" s="3" t="s">
+      <c r="AO4" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="AK4" s="3" t="s">
+      <c r="AP4" s="3" t="s">
         <v>612</v>
-      </c>
-      <c r="AL4" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="AM4" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="AN4" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="AO4" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="AP4" s="3" t="s">
-        <v>617</v>
       </c>
       <c r="AQ4" s="3" t="s">
         <v>347</v>
@@ -25775,13 +25746,13 @@
     </row>
     <row r="6" spans="1:60">
       <c r="A6" s="24" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D6" s="25">
         <v>9606</v>
@@ -25796,13 +25767,13 @@
         <v>427</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S6" s="15" t="s">
         <v>436</v>
@@ -25822,13 +25793,13 @@
     </row>
     <row r="7" spans="1:60">
       <c r="A7" s="24" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D7" s="27">
         <v>9606</v>
@@ -25843,13 +25814,13 @@
         <v>427</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S7" s="15" t="s">
         <v>436</v>
@@ -25869,13 +25840,13 @@
     </row>
     <row r="8" spans="1:60">
       <c r="A8" s="24" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D8" s="27">
         <v>9606</v>
@@ -25890,13 +25861,13 @@
         <v>427</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S8" s="15" t="s">
         <v>436</v>
@@ -25916,13 +25887,13 @@
     </row>
     <row r="9" spans="1:60">
       <c r="A9" s="24" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D9" s="27">
         <v>9606</v>
@@ -25937,13 +25908,13 @@
         <v>427</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S9" s="15" t="s">
         <v>436</v>
@@ -25963,13 +25934,13 @@
     </row>
     <row r="10" spans="1:60">
       <c r="A10" s="24" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D10" s="27">
         <v>9606</v>
@@ -25984,13 +25955,13 @@
         <v>427</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S10" s="15" t="s">
         <v>436</v>
@@ -26839,13 +26810,13 @@
   <sheetData>
     <row r="1" spans="1:82" ht="30" customHeight="1">
       <c r="A1" s="31" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>170</v>
@@ -26866,121 +26837,121 @@
         <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>459</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>667</v>
       </c>
       <c r="AW1" s="1" t="s">
         <v>183</v>
@@ -27022,19 +26993,19 @@
         <v>227</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="BK1" s="1" t="s">
         <v>450</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>228</v>
@@ -27114,19 +27085,19 @@
         <v>252</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>63</v>
@@ -27135,10 +27106,10 @@
         <v>64</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="S2" s="2" t="s">
         <v>63</v>
@@ -27147,10 +27118,10 @@
         <v>64</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>278</v>
@@ -27162,40 +27133,40 @@
         <v>64</v>
       </c>
       <c r="Z2" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="AE2" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>691</v>
       </c>
       <c r="AL2" s="2" t="s">
         <v>278</v>
@@ -27207,10 +27178,10 @@
         <v>64</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AQ2" s="2" t="s">
         <v>63</v>
@@ -27219,10 +27190,10 @@
         <v>64</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="AU2" s="2" t="s">
         <v>63</v>
@@ -27231,7 +27202,7 @@
         <v>64</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="AX2" s="2" t="s">
         <v>63</v>
@@ -27356,43 +27327,43 @@
         <v>298</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="P3" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="R3" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>332</v>
@@ -27404,64 +27375,64 @@
         <v>332</v>
       </c>
       <c r="Z3" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AG3" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AH3" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AI3" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AK3" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AL3" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AM3" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AN3" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="AO3" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AP3" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="AS3" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="AT3" s="2" t="s">
         <v>316</v>
@@ -27569,202 +27540,202 @@
     </row>
     <row r="4" spans="1:82">
       <c r="A4" s="32" t="s">
+        <v>716</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="Y4" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AD4" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AG4" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AH4" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AI4" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AK4" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AL4" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="AH4" s="3" t="s">
+      <c r="AM4" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="AI4" s="3" t="s">
+      <c r="AN4" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="AJ4" s="3" t="s">
+      <c r="AO4" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="AK4" s="3" t="s">
+      <c r="AP4" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="AL4" s="3" t="s">
+      <c r="AQ4" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="AM4" s="3" t="s">
+      <c r="AR4" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="AN4" s="3" t="s">
+      <c r="AS4" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="AO4" s="3" t="s">
+      <c r="AT4" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="AP4" s="3" t="s">
+      <c r="AU4" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="AQ4" s="3" t="s">
+      <c r="AV4" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="AR4" s="3" t="s">
+      <c r="AW4" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="AS4" s="3" t="s">
+      <c r="AX4" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="AT4" s="3" t="s">
+      <c r="AY4" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="AU4" s="3" t="s">
+      <c r="AZ4" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="AV4" s="3" t="s">
+      <c r="BA4" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="AW4" s="3" t="s">
+      <c r="BB4" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="AX4" s="3" t="s">
+      <c r="BC4" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="AY4" s="3" t="s">
+      <c r="BD4" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="AZ4" s="3" t="s">
+      <c r="BE4" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="BA4" s="3" t="s">
+      <c r="BF4" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="BB4" s="3" t="s">
+      <c r="BG4" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="BC4" s="3" t="s">
+      <c r="BH4" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="BD4" s="3" t="s">
+      <c r="BI4" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="BE4" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="BF4" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="BG4" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="BH4" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="BI4" s="3" t="s">
-        <v>781</v>
-      </c>
       <c r="BJ4" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="BK4" s="3" t="s">
         <v>486</v>
       </c>
       <c r="BL4" s="3" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="BM4" s="3" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="BN4" s="3" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="BO4" s="3" t="s">
         <v>408</v>
@@ -27903,13 +27874,13 @@
     </row>
     <row r="6" spans="1:82" ht="76">
       <c r="A6" s="33" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D6" s="34">
         <v>9606</v>
@@ -27920,7 +27891,7 @@
       <c r="H6" s="35"/>
       <c r="I6" s="35"/>
       <c r="J6" s="16" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="K6" s="35"/>
       <c r="L6" s="35"/>
@@ -27929,16 +27900,16 @@
       <c r="O6" s="35"/>
       <c r="P6" s="35"/>
       <c r="Q6" s="16" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="R6" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="S6" s="36" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="U6" s="35"/>
       <c r="V6" s="35"/>
@@ -27953,26 +27924,26 @@
         <v>36</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="AF6" s="16" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="AG6" s="35"/>
       <c r="AH6" s="35"/>
       <c r="AI6" s="35"/>
       <c r="AJ6" s="16" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="AK6" s="35"/>
       <c r="AL6" s="16" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="AM6" s="39" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="AN6" s="39" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="AO6" s="35"/>
       <c r="AP6" s="35"/>
@@ -27998,10 +27969,10 @@
         <v>427</v>
       </c>
       <c r="AZ6" s="6" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="BA6" s="40" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="BB6" s="41" t="s">
         <v>503</v>
@@ -28010,7 +27981,7 @@
         <v>27733501</v>
       </c>
       <c r="BD6" s="42" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="BE6" s="34"/>
       <c r="BF6" s="34"/>
@@ -28018,11 +27989,9 @@
       <c r="BH6" s="34"/>
       <c r="BI6" s="34"/>
       <c r="BJ6" s="33" t="s">
-        <v>618</v>
-      </c>
-      <c r="BK6" s="43" t="s">
-        <v>507</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="BK6" s="43"/>
       <c r="BL6" s="35"/>
       <c r="BM6" s="35"/>
       <c r="BN6" s="44"/>
@@ -28045,13 +28014,13 @@
     </row>
     <row r="7" spans="1:82" ht="76">
       <c r="A7" s="33" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D7" s="34">
         <v>9606</v>
@@ -28062,7 +28031,7 @@
       <c r="H7" s="35"/>
       <c r="I7" s="35"/>
       <c r="J7" s="16" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="K7" s="35"/>
       <c r="L7" s="35"/>
@@ -28071,16 +28040,16 @@
       <c r="O7" s="35"/>
       <c r="P7" s="35"/>
       <c r="Q7" s="16" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="S7" s="36" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="U7" s="35"/>
       <c r="V7" s="35"/>
@@ -28095,26 +28064,26 @@
         <v>42</v>
       </c>
       <c r="AE7" s="38" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="AF7" s="16" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="AG7" s="35"/>
       <c r="AH7" s="35"/>
       <c r="AI7" s="35"/>
       <c r="AJ7" s="16" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="AK7" s="35"/>
       <c r="AL7" s="16" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="AM7" s="39" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="AN7" s="39" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="AO7" s="35"/>
       <c r="AP7" s="35"/>
@@ -28140,10 +28109,10 @@
         <v>427</v>
       </c>
       <c r="AZ7" s="6" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="BA7" s="40" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="BB7" s="41" t="str">
         <f t="shared" ref="BB7:BB10" si="0">BB6</f>
@@ -28153,7 +28122,7 @@
         <v>27733501</v>
       </c>
       <c r="BD7" s="42" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="BE7" s="35"/>
       <c r="BF7" s="35"/>
@@ -28161,11 +28130,9 @@
       <c r="BH7" s="35"/>
       <c r="BI7" s="35"/>
       <c r="BJ7" s="33" t="s">
-        <v>623</v>
-      </c>
-      <c r="BK7" s="43" t="s">
-        <v>507</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="BK7" s="43"/>
       <c r="BL7" s="35"/>
       <c r="BM7" s="35"/>
       <c r="BN7" s="35"/>
@@ -28188,13 +28155,13 @@
     </row>
     <row r="8" spans="1:82" ht="76">
       <c r="A8" s="33" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D8" s="34">
         <v>9606</v>
@@ -28205,7 +28172,7 @@
       <c r="H8" s="35"/>
       <c r="I8" s="35"/>
       <c r="J8" s="16" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="K8" s="35"/>
       <c r="L8" s="35"/>
@@ -28214,16 +28181,16 @@
       <c r="O8" s="35"/>
       <c r="P8" s="35"/>
       <c r="Q8" s="16" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="R8" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="S8" s="36" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="U8" s="35"/>
       <c r="V8" s="35"/>
@@ -28238,26 +28205,26 @@
         <v>46</v>
       </c>
       <c r="AE8" s="38" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="AF8" s="16" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="AG8" s="35"/>
       <c r="AH8" s="35"/>
       <c r="AI8" s="35"/>
       <c r="AJ8" s="16" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="AK8" s="35"/>
       <c r="AL8" s="16" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="AM8" s="39" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="AN8" s="39" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="AO8" s="35"/>
       <c r="AP8" s="35"/>
@@ -28283,10 +28250,10 @@
         <v>427</v>
       </c>
       <c r="AZ8" s="6" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="BA8" s="40" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="BB8" s="41" t="str">
         <f t="shared" si="0"/>
@@ -28296,7 +28263,7 @@
         <v>27733501</v>
       </c>
       <c r="BD8" s="42" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="BE8" s="35"/>
       <c r="BF8" s="35"/>
@@ -28304,11 +28271,9 @@
       <c r="BH8" s="35"/>
       <c r="BI8" s="35"/>
       <c r="BJ8" s="33" t="s">
-        <v>624</v>
-      </c>
-      <c r="BK8" s="43" t="s">
-        <v>507</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="BK8" s="43"/>
       <c r="BL8" s="35"/>
       <c r="BM8" s="35"/>
       <c r="BN8" s="35"/>
@@ -28331,13 +28296,13 @@
     </row>
     <row r="9" spans="1:82" ht="76">
       <c r="A9" s="33" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D9" s="34">
         <v>9606</v>
@@ -28348,7 +28313,7 @@
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
       <c r="J9" s="16" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
@@ -28357,16 +28322,16 @@
       <c r="O9" s="35"/>
       <c r="P9" s="35"/>
       <c r="Q9" s="16" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="S9" s="36" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="U9" s="35"/>
       <c r="V9" s="35"/>
@@ -28379,26 +28344,26 @@
       <c r="AC9" s="35"/>
       <c r="AD9" s="37"/>
       <c r="AE9" s="38" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="AG9" s="35"/>
       <c r="AH9" s="35"/>
       <c r="AI9" s="35"/>
       <c r="AJ9" s="16" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="AK9" s="35"/>
       <c r="AL9" s="16" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="AM9" s="39" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="AN9" s="39" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="AO9" s="35"/>
       <c r="AP9" s="35"/>
@@ -28424,10 +28389,10 @@
         <v>427</v>
       </c>
       <c r="AZ9" s="6" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="BA9" s="40" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="BB9" s="41" t="str">
         <f t="shared" si="0"/>
@@ -28437,7 +28402,7 @@
         <v>27733501</v>
       </c>
       <c r="BD9" s="42" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="BE9" s="35"/>
       <c r="BF9" s="35"/>
@@ -28445,11 +28410,9 @@
       <c r="BH9" s="35"/>
       <c r="BI9" s="35"/>
       <c r="BJ9" s="33" t="s">
-        <v>625</v>
-      </c>
-      <c r="BK9" s="43" t="s">
-        <v>507</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="BK9" s="43"/>
       <c r="BL9" s="35"/>
       <c r="BM9" s="35"/>
       <c r="BN9" s="35"/>
@@ -28472,13 +28435,13 @@
     </row>
     <row r="10" spans="1:82" ht="76">
       <c r="A10" s="33" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D10" s="34">
         <v>9606</v>
@@ -28489,7 +28452,7 @@
       <c r="H10" s="35"/>
       <c r="I10" s="35"/>
       <c r="J10" s="16" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="K10" s="35"/>
       <c r="L10" s="35"/>
@@ -28498,16 +28461,16 @@
       <c r="O10" s="35"/>
       <c r="P10" s="35"/>
       <c r="Q10" s="16" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="R10" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="S10" s="36" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="U10" s="35"/>
       <c r="V10" s="35"/>
@@ -28522,26 +28485,26 @@
         <v>32</v>
       </c>
       <c r="AE10" s="38" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="AF10" s="16" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="AG10" s="35"/>
       <c r="AH10" s="35"/>
       <c r="AI10" s="35"/>
       <c r="AJ10" s="16" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="AK10" s="35"/>
       <c r="AL10" s="16" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="AM10" s="39" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="AN10" s="39" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="AO10" s="35"/>
       <c r="AP10" s="35"/>
@@ -28567,10 +28530,10 @@
         <v>427</v>
       </c>
       <c r="AZ10" s="6" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="BA10" s="40" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="BB10" s="41" t="str">
         <f t="shared" si="0"/>
@@ -28580,7 +28543,7 @@
         <v>27733501</v>
       </c>
       <c r="BD10" s="42" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="BE10" s="35"/>
       <c r="BF10" s="35"/>
@@ -28588,11 +28551,9 @@
       <c r="BH10" s="35"/>
       <c r="BI10" s="35"/>
       <c r="BJ10" s="33" t="s">
-        <v>626</v>
-      </c>
-      <c r="BK10" s="43" t="s">
-        <v>507</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="BK10" s="43"/>
       <c r="BL10" s="35"/>
       <c r="BM10" s="35"/>
       <c r="BN10" s="35"/>
@@ -28868,13 +28829,13 @@
   <sheetData>
     <row r="1" spans="1:50" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>170</v>
@@ -28904,70 +28865,70 @@
         <v>185</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>819</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>824</v>
       </c>
       <c r="AI1" s="1" t="s">
         <v>228</v>
@@ -29047,7 +29008,7 @@
         <v>252</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>63</v>
@@ -29056,7 +29017,7 @@
         <v>64</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>63</v>
@@ -29065,7 +29026,7 @@
         <v>64</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>63</v>
@@ -29074,7 +29035,7 @@
         <v>64</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>260</v>
@@ -29086,7 +29047,7 @@
         <v>64</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>278</v>
@@ -29098,19 +29059,19 @@
         <v>64</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>244</v>
@@ -29202,25 +29163,25 @@
         <v>305</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>310</v>
@@ -29244,19 +29205,19 @@
         <v>332</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="AF3" s="2"/>
       <c r="AG3" s="2" t="s">
@@ -29310,106 +29271,106 @@
     </row>
     <row r="4" spans="1:50" hidden="1">
       <c r="A4" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="Y4" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AD4" s="3" t="s">
         <v>863</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="AG4" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AH4" s="3" t="s">
         <v>866</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="AD4" s="3" t="s">
-        <v>868</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>869</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="AH4" s="3" t="s">
-        <v>871</v>
       </c>
       <c r="AI4" s="3" t="s">
         <v>408</v>
